--- a/sources/Xtb.Toolkit.Demo/report.xlsx
+++ b/sources/Xtb.Toolkit.Demo/report.xlsx
@@ -1,33 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Cash Operations" r:id="rId3" sheetId="1"/>
-    <sheet name="Closed Positions" r:id="rId4" sheetId="2"/>
+    <sheet name="Cash Operations" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Closed Positions" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t xml:space="preserve">Account number</t>
   </si>
   <si>
-    <t xml:space="preserve">2841235</t>
+    <t xml:space="preserve">2141536</t>
   </si>
   <si>
     <t xml:space="preserve">Cash Operations</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">Date from (UTC)</t>
   </si>
   <si>
@@ -67,25 +71,25 @@
     <t xml:space="preserve">Core MSCI World</t>
   </si>
   <si>
-    <t xml:space="preserve">1249219227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN BUY 8/8.4907 @ 117.775</t>
+    <t xml:space="preserve">1237295327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN BUY 8/8.4907 @ 110.775</t>
   </si>
   <si>
     <t xml:space="preserve">My Trades</t>
   </si>
   <si>
-    <t xml:space="preserve">1249219221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN BUY 0.4907/8.4907 @ 117.775</t>
+    <t xml:space="preserve">1237295321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN BUY 0.4907/8.4907 @ 110.775</t>
   </si>
   <si>
     <t xml:space="preserve">Free funds interest</t>
   </si>
   <si>
-    <t xml:space="preserve">1246946760</t>
+    <t xml:space="preserve">1244793269</t>
   </si>
   <si>
     <t xml:space="preserve">Free-funds Interest 2026-04</t>
@@ -167,25 +171,45 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
-      <sz val="11.00"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.00"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.00"/>
-      <color rgb="FF0000"/>
-      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,7 +221,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -205,183 +229,322 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <dxfs count="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="33.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="37.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.84"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>4</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>46142.875</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46173.8749999884</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>46173.874999988424</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="B6" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="2" t="n">
+        <v>46149.4465393519</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>-942.2</v>
+      </c>
+      <c r="F6" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>46146.529877326386</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-942.2</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="H6" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>46149.4465162037</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>-57.79</v>
+      </c>
+      <c r="F7" s="0" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>46146.52985225694</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-57.79</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
+      <c r="D8" s="2" t="n">
+        <v>46146.2930320602</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F8" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>46146.29303206019</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>25</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>-998.33</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -390,150 +553,148 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="17.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="24.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="25.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="15.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="14.11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>4</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>46142.875</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46173.8749999884</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>46173.874999988424</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="Y5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
